--- a/Data/testDataPT_IDGenerator.xlsx
+++ b/Data/testDataPT_IDGenerator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\WorkdayPlaywright\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B2F093-0112-4CC8-B0A5-8F5DD651E062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDAFCB85-5BA5-4994-BBE1-5ECC19ECCBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="78">
   <si>
     <t>Country1</t>
   </si>
@@ -261,6 +261,15 @@
   </si>
   <si>
     <t>24982928 2AP25</t>
+  </si>
+  <si>
+    <t>24982928 2AP26</t>
+  </si>
+  <si>
+    <t>24982928 2AP27</t>
+  </si>
+  <si>
+    <t>24982928 2AP28</t>
   </si>
 </sst>
 </file>
@@ -662,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="9" width="15.33203125" customWidth="1"/>
@@ -777,7 +786,7 @@
         <v>57</v>
       </c>
       <c r="N3" t="str">
-        <f t="shared" ref="N3:N61" si="0">K3&amp;" "&amp;L3&amp;M3</f>
+        <f t="shared" ref="N3:N64" si="0">K3&amp;" "&amp;L3&amp;M3</f>
         <v>24982928 2AO57</v>
       </c>
     </row>
@@ -3215,6 +3224,132 @@
       <c r="N61" t="str">
         <f t="shared" si="0"/>
         <v>24982928 2AP25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="6">
+        <v>10000085213.809601</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="6">
+        <v>100035413.80951899</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="K62" s="6">
+        <v>24982928</v>
+      </c>
+      <c r="L62" t="s">
+        <v>44</v>
+      </c>
+      <c r="M62">
+        <v>26</v>
+      </c>
+      <c r="N62" t="str">
+        <f t="shared" si="0"/>
+        <v>24982928 2AP26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="6">
+        <v>10000070927.095301</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F63" s="6">
+        <v>100021127.09523299</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="K63" s="6">
+        <v>24982928</v>
+      </c>
+      <c r="L63" t="s">
+        <v>44</v>
+      </c>
+      <c r="M63">
+        <v>27</v>
+      </c>
+      <c r="N63" t="str">
+        <f t="shared" si="0"/>
+        <v>24982928 2AP27</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="6">
+        <v>10000056640.381001</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="6">
+        <v>100006840.38094699</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="K64" s="6">
+        <v>24982928</v>
+      </c>
+      <c r="L64" t="s">
+        <v>44</v>
+      </c>
+      <c r="M64">
+        <v>28</v>
+      </c>
+      <c r="N64" t="str">
+        <f t="shared" si="0"/>
+        <v>24982928 2AP28</v>
       </c>
     </row>
   </sheetData>
